--- a/PubChem_output2.xlsx
+++ b/PubChem_output2.xlsx
@@ -521,22 +521,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Flammable
-Irritant</t>
+          <t>Irritant
+Flammable</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+          <t>H320: Causes eye irritation [Warning Serious eye damage/eye irritation]
+H225: Highly Flammable liquid and vapor [Danger Flammable liquids]
+H225 (94%): Highly Flammable liquid and vapor [Danger Flammable liquids]
+H336: May cause drowsiness or dizziness [Warning Specific target organ toxicity, single exposure; Narcotic effects]
+H336 (15.4%): May cause drowsiness or dizziness [Warning Specific target organ toxicity, single exposure; Narcotic effects]
+H332: Harmful if inhaled [Warning Acute toxicity, inhalation]
 H316: Causes mild skin irritation [Warning Skin corrosion/irritation]
-H320: Causes eye irritation [Warning Serious eye damage/eye irritation]
-H332: Harmful if inhaled [Warning Acute toxicity, inhalation]
-H333: May be harmful if inhaled [Warning Acute toxicity, inhalation]
-H336: May cause drowsiness or dizziness [Warning Specific target organ toxicity, single exposure; Narcotic effects]
 H402: Harmful to aquatic life [Hazardous to the aquatic environment, acute hazard]
-H225: Highly Flammable liquid and vapor [Danger Flammable liquids]
-H336 (15.4%): May cause drowsiness or dizziness [Warning Specific target organ toxicity, single exposure; Narcotic effects]
-H225 (94%): Highly Flammable liquid and vapor [Danger Flammable liquids]</t>
+H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+H333: May be harmful if inhaled [Warning Acute toxicity, inhalation]</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,8 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1733-13-7</t>
+          <t>8004-87-3
+1733-13-7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -645,16 +646,16 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Flammable
-Irritant</t>
+          <t>Irritant
+Flammable</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>H226: Flammable liquid and vapor [Warning Flammable liquids]
 H332: Harmful if inhaled [Warning Acute toxicity, inhalation]
-H226 (100%): Flammable liquid and vapor [Warning Flammable liquids]
-H332 (100%): Harmful if inhaled [Warning Acute toxicity, inhalation]</t>
+H332 (100%): Harmful if inhaled [Warning Acute toxicity, inhalation]
+H226 (100%): Flammable liquid and vapor [Warning Flammable liquids]</t>
         </is>
       </c>
     </row>
@@ -706,39 +707,39 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Acute Toxic
-Corrosive
+          <t>Corrosive
+Flammable
 Environmental Hazard
 Irritant
 Health Hazard
-Flammable</t>
+Acute Toxic</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>H373: May causes damage to organs through prolonged or repeated exposure [Warning Specific target organ toxicity, repeated exposure]
+          <t>H335 (38.7%): May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+H319: Causes serious eye irritation [Warning Serious eye damage/eye irritation]
+H318: Causes serious eye damage [Danger Serious eye damage/eye irritation]
+H302 (100%): Harmful if swallowed [Warning Acute toxicity, oral]
+H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+H228: Flammable solid [Danger Flammable solids]
+H302: Harmful if swallowed [Warning Acute toxicity, oral]
+H332 (14.8%): Harmful if inhaled [Warning Acute toxicity, inhalation]
+H312: Harmful in contact with skin [Warning Acute toxicity, dermal]
+H311: Toxic in contact with skin [Danger Acute toxicity, dermal]
 H401: Toxic to aquatic life [Hazardous to the aquatic environment, acute hazard]
-H302: Harmful if swallowed [Warning Acute toxicity, oral]
-H302 (100%): Harmful if swallowed [Warning Acute toxicity, oral]
-H302 (93.7%): Harmful if swallowed [Warning Acute toxicity, oral]
-H400: Very toxic to aquatic life [Warning Hazardous to the aquatic environment, acute hazard]
-H315 (98.2%): Causes skin irritation [Warning Skin corrosion/irritation]
-H318: Causes serious eye damage [Danger Serious eye damage/eye irritation]
-H412: Harmful to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]
+H373: May causes damage to organs through prolonged or repeated exposure [Warning Specific target organ toxicity, repeated exposure]
+H370: Causes damage to organs [Danger Specific target organ toxicity, single exposure]
+H318 (52.3%): Causes serious eye damage [Danger Serious eye damage/eye irritation]
+H412 (40.2%): Harmful to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]
 H310: Fatal in contact with skin [Danger Acute toxicity, dermal]
-H311: Toxic in contact with skin [Danger Acute toxicity, dermal]
-H335 (38.7%): May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
-H319: Causes serious eye irritation [Warning Serious eye damage/eye irritation]
-H228 (38.9%): Flammable solid [Danger Flammable solids]
-H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
 H319 (39.8%): Causes serious eye irritation [Warning Serious eye damage/eye irritation]
 H315: Causes skin irritation [Warning Skin corrosion/irritation]
-H332 (14.8%): Harmful if inhaled [Warning Acute toxicity, inhalation]
-H228: Flammable solid [Danger Flammable solids]
-H412 (40.2%): Harmful to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]
-H312: Harmful in contact with skin [Warning Acute toxicity, dermal]
-H318 (52.3%): Causes serious eye damage [Danger Serious eye damage/eye irritation]
-H370: Causes damage to organs [Danger Specific target organ toxicity, single exposure]</t>
+H302 (93.7%): Harmful if swallowed [Warning Acute toxicity, oral]
+H315 (98.2%): Causes skin irritation [Warning Skin corrosion/irritation]
+H412: Harmful to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]
+H400: Very toxic to aquatic life [Warning Hazardous to the aquatic environment, acute hazard]
+H228 (38.9%): Flammable solid [Danger Flammable solids]</t>
         </is>
       </c>
     </row>
@@ -790,19 +791,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Oxidizer
+          <t>Corrosive
 Irritant
-Corrosive
+Oxidizer
 Health Hazard</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>H314: Causes severe skin burns and eye damage [Danger Skin corrosion/irritation]
-H371: May cause damage to organs [Warning Specific target organ toxicity, single exposure]
+          <t>H302: Harmful if swallowed [Warning Acute toxicity, oral]
+H272 (100%): May intensify fire; oxidizer [Danger Oxidizing liquids; Oxidizing solids]
 H314 (100%): Causes severe skin burns and eye damage [Danger Skin corrosion/irritation]
-H272 (100%): May intensify fire; oxidizer [Danger Oxidizing liquids; Oxidizing solids]
-H302: Harmful if swallowed [Warning Acute toxicity, oral]</t>
+H314: Causes severe skin burns and eye damage [Danger Skin corrosion/irritation]
+H371: May cause damage to organs [Warning Specific target organ toxicity, single exposure]</t>
         </is>
       </c>
     </row>
@@ -856,34 +857,34 @@
         <is>
           <t>Corrosive
 Environmental Hazard
-Acute Toxic
 Irritant
-Health Hazard</t>
+Health Hazard
+Acute Toxic</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>H372: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
+          <t>H319: Causes serious eye irritation [Warning Serious eye damage/eye irritation]
+H360D ***: May damage the unborn child [Danger Reproductive toxicity]
+H360FD: May damage fertility; May damage the unborn child [Danger Reproductive toxicity]
+H360D (10.5%): May damage the unborn child [Danger Reproductive toxicity]
+H410: Very toxic to aquatic life with long lasting effects [Warning Hazardous to the aquatic environment, long-term hazard]
+H330: Fatal if inhaled [Danger Acute toxicity, inhalation]
+H410 (100%): Very toxic to aquatic life with long lasting effects [Warning Hazardous to the aquatic environment, long-term hazard]
+H290 (18.2%): May be corrosive to metals [Warning Corrosive to Metals]
+H400 (97.4%): Very toxic to aquatic life [Warning Hazardous to the aquatic environment, acute hazard]
+H330 (98.6%): Fatal if inhaled [Danger Acute toxicity, inhalation]
+H360 (88.2%): May damage fertility or the unborn child [Danger Reproductive toxicity]
+H300+H330 (10%): Fatal if swallowed or if inhaled [Danger Acute toxicity, oral; acute toxicity, inhalation]
+H300 (36.7%): Fatal if swallowed [Danger Acute toxicity, oral]
+H341: Suspected of causing genetic defects [Warning Germ cell mutagenicity]
+H317: May cause an allergic skin reaction [Warning Sensitization, Skin]
+H370: Causes damage to organs [Danger Specific target organ toxicity, single exposure]
+H372 **: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
+H372 (98.8%): Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
 H360: May damage fertility or the unborn child [Danger Reproductive toxicity]
-H300+H330 (10%): Fatal if swallowed or if inhaled [Danger Acute toxicity, oral; acute toxicity, inhalation]
-H360 (88.2%): May damage fertility or the unborn child [Danger Reproductive toxicity]
-H410 (100%): Very toxic to aquatic life with long lasting effects [Warning Hazardous to the aquatic environment, long-term hazard]
 H400: Very toxic to aquatic life [Warning Hazardous to the aquatic environment, acute hazard]
-H400 (97.4%): Very toxic to aquatic life [Warning Hazardous to the aquatic environment, acute hazard]
-H360FD: May damage fertility; May damage the unborn child [Danger Reproductive toxicity]
-H319: Causes serious eye irritation [Warning Serious eye damage/eye irritation]
-H372 (98.8%): Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
-H341: Suspected of causing genetic defects [Warning Germ cell mutagenicity]
-H360D ***: May damage the unborn child [Danger Reproductive toxicity]
-H317: May cause an allergic skin reaction [Warning Sensitization, Skin]
-H290 (18.2%): May be corrosive to metals [Warning Corrosive to Metals]
-H330 (98.6%): Fatal if inhaled [Danger Acute toxicity, inhalation]
-H372 **: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
-H330: Fatal if inhaled [Danger Acute toxicity, inhalation]
-H410: Very toxic to aquatic life with long lasting effects [Warning Hazardous to the aquatic environment, long-term hazard]
-H300 (36.7%): Fatal if swallowed [Danger Acute toxicity, oral]
-H370: Causes damage to organs [Danger Specific target organ toxicity, single exposure]
-H360D (10.5%): May damage the unborn child [Danger Reproductive toxicity]</t>
+H372: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]</t>
         </is>
       </c>
     </row>
@@ -935,27 +936,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Environmental Hazard
-Irritant
+          <t>Irritant
+Environmental Hazard
 Health Hazard</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>H362: May cause harm to breast-fed children [Reproductive toxicity, effects on or via lactation]
-H361: Suspected of damaging fertility or the unborn child [Warning Reproductive toxicity]
+          <t>H334 (11.7%): May cause allergy or asthma symptoms or breathing difficulties if inhaled [Danger Sensitization, respiratory]
 H320: Causes eye irritation [Warning Serious eye damage/eye irritation]
 H370: Causes damage to organs [Danger Specific target organ toxicity, single exposure]
-H373 (11.4%): May causes damage to organs through prolonged or repeated exposure [Warning Specific target organ toxicity, repeated exposure]
+H360: May damage fertility or the unborn child [Danger Reproductive toxicity]
+H361: Suspected of damaging fertility or the unborn child [Warning Reproductive toxicity]
+H319 (30.1%): Causes serious eye irritation [Warning Serious eye damage/eye irritation]
+H372 (43.6%): Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
 H411 (14%): Toxic to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]
+H317 (20.8%): May cause an allergic skin reaction [Warning Sensitization, Skin]
+H362: May cause harm to breast-fed children [Reproductive toxicity, effects on or via lactation]
+H372: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
 H315 (28.4%): Causes skin irritation [Warning Skin corrosion/irritation]
-H372 (43.6%): Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
-H372: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
-H334 (11.7%): May cause allergy or asthma symptoms or breathing difficulties if inhaled [Danger Sensitization, respiratory]
 H302 (16.2%): Harmful if swallowed [Warning Acute toxicity, oral]
-H360: May damage fertility or the unborn child [Danger Reproductive toxicity]
-H317 (20.8%): May cause an allergic skin reaction [Warning Sensitization, Skin]
-H319 (30.1%): Causes serious eye irritation [Warning Serious eye damage/eye irritation]</t>
+H373 (11.4%): May causes damage to organs through prolonged or repeated exposure [Warning Specific target organ toxicity, repeated exposure]</t>
         </is>
       </c>
     </row>
@@ -1049,8 +1050,8 @@
         <is>
           <t>131-54-4
 2,2'-Dihydroxy-4,4'-dimethoxybenzophenone
+Bis(2-hydroxy-4-methoxyphenyl)methanone
 Benzophenone-6
-Bis(2-hydroxy-4-methoxyphenyl)methanone
 Methanone, bis(2-hydroxy-4-methoxyphenyl)-</t>
         </is>
       </c>
@@ -1062,10 +1063,10 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>H319 (20.1%): Causes serious eye irritation [Warning Serious eye damage/eye irritation]
-H315 (20.1%): Causes skin irritation [Warning Skin corrosion/irritation]
-H335 (19.6%): May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
-H411 (50.9%): Toxic to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]</t>
+          <t>H315 (20.1%): Causes skin irritation [Warning Skin corrosion/irritation]
+H319 (20.1%): Causes serious eye irritation [Warning Serious eye damage/eye irritation]
+H411 (50.9%): Toxic to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]
+H335 (19.6%): May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]</t>
         </is>
       </c>
     </row>
